--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** ValueSet für zulässige Ausprägungen des elements emptyReason Status eines Medikationsplaneintrags (MedicationRequest).</t>
+    <t>ValueSet für zulässige Ausprägungen des elements emptyReason Status eines Medikationsplaneintrags (MedicationRequest).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-MedikationsplanEmptyReasonVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
